--- a/data/rpe_femenil.xlsx
+++ b/data/rpe_femenil.xlsx
@@ -134,6 +134,9 @@
     <t>Luna</t>
   </si>
   <si>
+    <t>Marca temporal</t>
+  </si>
+  <si>
     <t>Karen Luna</t>
   </si>
   <si>
@@ -141,9 +144,6 @@
   </si>
   <si>
     <t>Sarah Luebbert</t>
-  </si>
-  <si>
-    <t>Marca temporal</t>
   </si>
   <si>
     <t>Aylin</t>
@@ -767,7 +767,7 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>43</v>
+        <v>40</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>53</v>
@@ -15312,7 +15312,7 @@
         <v>71</v>
       </c>
       <c r="D633" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E633" s="12" t="s">
         <v>67</v>
@@ -15473,7 +15473,7 @@
         <v>88</v>
       </c>
       <c r="D640" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E640" s="12" t="s">
         <v>75</v>
@@ -16002,7 +16002,7 @@
         <v>71</v>
       </c>
       <c r="D663" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E663" s="12" t="s">
         <v>65</v>
@@ -16140,7 +16140,7 @@
         <v>74</v>
       </c>
       <c r="D669" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E669" s="12" t="s">
         <v>66</v>
@@ -16255,7 +16255,7 @@
         <v>88</v>
       </c>
       <c r="D674" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E674" s="12" t="s">
         <v>87</v>
@@ -16715,7 +16715,7 @@
         <v>64</v>
       </c>
       <c r="D694" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E694" s="12" t="s">
         <v>66</v>
@@ -16945,7 +16945,7 @@
         <v>59</v>
       </c>
       <c r="D704" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E704" s="12" t="s">
         <v>65</v>
@@ -17612,7 +17612,7 @@
         <v>86</v>
       </c>
       <c r="D733" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E733" s="12" t="s">
         <v>72</v>
@@ -17911,7 +17911,7 @@
         <v>71</v>
       </c>
       <c r="D746" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E746" s="12" t="s">
         <v>75</v>
@@ -18394,7 +18394,7 @@
         <v>76</v>
       </c>
       <c r="D767" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E767" s="12" t="s">
         <v>68</v>
@@ -19061,7 +19061,7 @@
         <v>64</v>
       </c>
       <c r="D796" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E796" s="12" t="s">
         <v>67</v>
@@ -19337,7 +19337,7 @@
         <v>86</v>
       </c>
       <c r="D808" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E808" s="12" t="s">
         <v>77</v>
@@ -19590,7 +19590,7 @@
         <v>71</v>
       </c>
       <c r="D819" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E819" s="12" t="s">
         <v>75</v>
@@ -20188,7 +20188,7 @@
         <v>88</v>
       </c>
       <c r="D845" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E845" s="12" t="s">
         <v>72</v>
@@ -20510,7 +20510,7 @@
         <v>76</v>
       </c>
       <c r="D859" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E859" s="12" t="s">
         <v>67</v>
@@ -20924,7 +20924,7 @@
         <v>59</v>
       </c>
       <c r="D877" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E877" s="12" t="s">
         <v>66</v>
@@ -21246,7 +21246,7 @@
         <v>86</v>
       </c>
       <c r="D891" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E891" s="12" t="s">
         <v>61</v>
@@ -21936,7 +21936,7 @@
         <v>71</v>
       </c>
       <c r="D921" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E921" s="12" t="s">
         <v>66</v>
@@ -22327,7 +22327,7 @@
         <v>74</v>
       </c>
       <c r="D938" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E938" s="12" t="s">
         <v>68</v>
@@ -22534,7 +22534,7 @@
         <v>64</v>
       </c>
       <c r="D947" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E947" s="12" t="s">
         <v>61</v>
@@ -22649,7 +22649,7 @@
         <v>64</v>
       </c>
       <c r="D952" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E952" s="12" t="s">
         <v>65</v>
@@ -22948,7 +22948,7 @@
         <v>59</v>
       </c>
       <c r="D965" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E965" s="12" t="s">
         <v>61</v>
@@ -23086,7 +23086,7 @@
         <v>59</v>
       </c>
       <c r="D971" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E971" s="12" t="s">
         <v>68</v>
@@ -23454,7 +23454,7 @@
         <v>86</v>
       </c>
       <c r="D987" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E987" s="12" t="s">
         <v>65</v>
@@ -23684,7 +23684,7 @@
         <v>86</v>
       </c>
       <c r="D997" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E997" s="12" t="s">
         <v>68</v>
@@ -23960,7 +23960,7 @@
         <v>71</v>
       </c>
       <c r="D1009" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1009" s="12" t="s">
         <v>72</v>
@@ -24190,7 +24190,7 @@
         <v>71</v>
       </c>
       <c r="D1019" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1019" s="12" t="s">
         <v>68</v>
@@ -24696,7 +24696,7 @@
         <v>74</v>
       </c>
       <c r="D1041" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1041" s="12" t="s">
         <v>68</v>
@@ -24926,7 +24926,7 @@
         <v>88</v>
       </c>
       <c r="D1051" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1051" s="12" t="s">
         <v>68</v>
@@ -25041,7 +25041,7 @@
         <v>88</v>
       </c>
       <c r="D1056" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1056" s="12" t="s">
         <v>65</v>
@@ -25202,7 +25202,7 @@
         <v>76</v>
       </c>
       <c r="D1063" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1063" s="12" t="s">
         <v>61</v>
@@ -25409,7 +25409,7 @@
         <v>76</v>
       </c>
       <c r="D1072" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1072" s="12" t="s">
         <v>68</v>
@@ -25938,7 +25938,7 @@
         <v>64</v>
       </c>
       <c r="D1095" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1095" s="12" t="s">
         <v>68</v>
@@ -26260,7 +26260,7 @@
         <v>64</v>
       </c>
       <c r="D1109" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1109" s="12" t="s">
         <v>66</v>
@@ -26467,7 +26467,7 @@
         <v>59</v>
       </c>
       <c r="D1118" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1118" s="12" t="s">
         <v>67</v>
@@ -26950,7 +26950,7 @@
         <v>71</v>
       </c>
       <c r="D1139" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1139" s="12" t="s">
         <v>77</v>
@@ -27019,7 +27019,7 @@
         <v>71</v>
       </c>
       <c r="D1142" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1142" s="12" t="s">
         <v>61</v>
@@ -27502,7 +27502,7 @@
         <v>74</v>
       </c>
       <c r="D1163" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1163" s="12" t="s">
         <v>67</v>
@@ -27525,7 +27525,7 @@
         <v>74</v>
       </c>
       <c r="D1164" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1164" s="12" t="s">
         <v>66</v>
@@ -27985,7 +27985,7 @@
         <v>88</v>
       </c>
       <c r="D1184" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1184" s="12" t="s">
         <v>67</v>
@@ -28353,7 +28353,7 @@
         <v>64</v>
       </c>
       <c r="D1200" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1200" s="12" t="s">
         <v>61</v>
@@ -28399,7 +28399,7 @@
         <v>64</v>
       </c>
       <c r="D1202" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1202" s="12" t="s">
         <v>65</v>
@@ -28652,7 +28652,7 @@
         <v>59</v>
       </c>
       <c r="D1213" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1213" s="12" t="s">
         <v>67</v>
@@ -28721,7 +28721,7 @@
         <v>59</v>
       </c>
       <c r="D1216" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1216" s="12" t="s">
         <v>65</v>
@@ -29066,7 +29066,7 @@
         <v>86</v>
       </c>
       <c r="D1231" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1231" s="12" t="s">
         <v>65</v>
@@ -29342,7 +29342,7 @@
         <v>86</v>
       </c>
       <c r="D1243" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1243" s="12" t="s">
         <v>65</v>
@@ -29595,7 +29595,7 @@
         <v>71</v>
       </c>
       <c r="D1254" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1254" s="12" t="s">
         <v>66</v>
@@ -29894,7 +29894,7 @@
         <v>71</v>
       </c>
       <c r="D1267" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1267" s="12" t="s">
         <v>66</v>
@@ -30262,7 +30262,7 @@
         <v>74</v>
       </c>
       <c r="D1283" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1283" s="12" t="s">
         <v>68</v>
@@ -30584,7 +30584,7 @@
         <v>76</v>
       </c>
       <c r="D1297" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1297" s="12" t="s">
         <v>65</v>
@@ -30676,7 +30676,7 @@
         <v>76</v>
       </c>
       <c r="D1301" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1301" s="12" t="s">
         <v>65</v>
@@ -30791,7 +30791,7 @@
         <v>64</v>
       </c>
       <c r="D1306" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1306" s="12" t="s">
         <v>65</v>
@@ -30952,7 +30952,7 @@
         <v>64</v>
       </c>
       <c r="D1313" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1313" s="12" t="s">
         <v>68</v>
@@ -31389,7 +31389,7 @@
         <v>59</v>
       </c>
       <c r="D1332" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1332" s="12" t="s">
         <v>68</v>
@@ -31504,7 +31504,7 @@
         <v>59</v>
       </c>
       <c r="D1337" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1337" s="12" t="s">
         <v>65</v>
@@ -31665,7 +31665,7 @@
         <v>71</v>
       </c>
       <c r="D1344" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1344" s="12" t="s">
         <v>61</v>
@@ -31941,7 +31941,7 @@
         <v>71</v>
       </c>
       <c r="D1356" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1356" s="12" t="s">
         <v>66</v>
@@ -32286,7 +32286,7 @@
         <v>64</v>
       </c>
       <c r="D1371" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1371" s="12" t="s">
         <v>65</v>
@@ -32493,7 +32493,7 @@
         <v>64</v>
       </c>
       <c r="D1380" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1380" s="12" t="s">
         <v>66</v>
@@ -32792,7 +32792,7 @@
         <v>88</v>
       </c>
       <c r="D1393" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1393" s="12" t="s">
         <v>61</v>
@@ -32884,7 +32884,7 @@
         <v>88</v>
       </c>
       <c r="D1397" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1397" s="12" t="s">
         <v>66</v>
@@ -32976,7 +32976,7 @@
         <v>76</v>
       </c>
       <c r="D1401" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1401" s="12" t="s">
         <v>68</v>
@@ -33137,7 +33137,7 @@
         <v>76</v>
       </c>
       <c r="D1408" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1408" s="12" t="s">
         <v>68</v>
@@ -33229,7 +33229,7 @@
         <v>59</v>
       </c>
       <c r="D1412" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1412" s="12" t="s">
         <v>61</v>
@@ -33390,7 +33390,7 @@
         <v>59</v>
       </c>
       <c r="D1419" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1419" s="12" t="s">
         <v>65</v>
@@ -33574,7 +33574,7 @@
         <v>86</v>
       </c>
       <c r="D1427" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1427" s="12" t="s">
         <v>66</v>
@@ -33873,7 +33873,7 @@
         <v>86</v>
       </c>
       <c r="D1440" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1440" s="12" t="s">
         <v>68</v>
@@ -34126,7 +34126,7 @@
         <v>74</v>
       </c>
       <c r="D1451" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1451" s="12" t="s">
         <v>72</v>
@@ -34747,7 +34747,7 @@
         <v>88</v>
       </c>
       <c r="D1478" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1478" s="12" t="s">
         <v>77</v>
@@ -35483,7 +35483,7 @@
         <v>59</v>
       </c>
       <c r="D1510" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1510" s="12" t="s">
         <v>66</v>
@@ -36012,7 +36012,7 @@
         <v>71</v>
       </c>
       <c r="D1533" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1533" s="12" t="s">
         <v>61</v>
@@ -36334,7 +36334,7 @@
         <v>74</v>
       </c>
       <c r="D1547" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1547" s="12" t="s">
         <v>66</v>
@@ -36449,7 +36449,7 @@
         <v>88</v>
       </c>
       <c r="D1552" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1552" s="12" t="s">
         <v>93</v>
@@ -37024,7 +37024,7 @@
         <v>59</v>
       </c>
       <c r="D1577" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1577" s="12" t="s">
         <v>61</v>
@@ -37369,7 +37369,7 @@
         <v>86</v>
       </c>
       <c r="D1592" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1592" s="12" t="s">
         <v>65</v>
@@ -37553,7 +37553,7 @@
         <v>71</v>
       </c>
       <c r="D1600" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1600" s="12" t="s">
         <v>61</v>
@@ -37599,7 +37599,7 @@
         <v>71</v>
       </c>
       <c r="D1602" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1602" s="12" t="s">
         <v>66</v>
@@ -37898,7 +37898,7 @@
         <v>71</v>
       </c>
       <c r="D1615" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1615" s="12" t="s">
         <v>66</v>
@@ -38542,7 +38542,7 @@
         <v>88</v>
       </c>
       <c r="D1643" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1643" s="12" t="s">
         <v>66</v>
@@ -38818,7 +38818,7 @@
         <v>76</v>
       </c>
       <c r="D1655" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1655" s="12" t="s">
         <v>66</v>
@@ -39117,7 +39117,7 @@
         <v>64</v>
       </c>
       <c r="D1668" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1668" s="12" t="s">
         <v>75</v>
@@ -39370,7 +39370,7 @@
         <v>71</v>
       </c>
       <c r="D1679" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1679" s="12" t="s">
         <v>61</v>
@@ -39692,7 +39692,7 @@
         <v>88</v>
       </c>
       <c r="D1693" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1693" s="12" t="s">
         <v>61</v>
@@ -39899,7 +39899,7 @@
         <v>76</v>
       </c>
       <c r="D1702" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1702" s="12" t="s">
         <v>66</v>
@@ -40313,7 +40313,7 @@
         <v>64</v>
       </c>
       <c r="D1720" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1720" s="12" t="s">
         <v>68</v>
@@ -41072,7 +41072,7 @@
         <v>86</v>
       </c>
       <c r="D1753" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1753" s="12" t="s">
         <v>66</v>
@@ -41877,7 +41877,7 @@
         <v>64</v>
       </c>
       <c r="D1788" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1788" s="12" t="s">
         <v>66</v>
@@ -41992,7 +41992,7 @@
         <v>59</v>
       </c>
       <c r="D1793" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1793" s="12" t="s">
         <v>68</v>
@@ -42682,7 +42682,7 @@
         <v>76</v>
       </c>
       <c r="D1823" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1823" s="12" t="s">
         <v>65</v>
@@ -42705,7 +42705,7 @@
         <v>76</v>
       </c>
       <c r="D1824" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1824" s="12" t="s">
         <v>68</v>
@@ -42843,7 +42843,7 @@
         <v>64</v>
       </c>
       <c r="D1830" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1830" s="12" t="s">
         <v>65</v>
@@ -42935,7 +42935,7 @@
         <v>64</v>
       </c>
       <c r="D1834" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1834" s="12" t="s">
         <v>68</v>
@@ -43211,7 +43211,7 @@
         <v>88</v>
       </c>
       <c r="D1846" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1846" s="12" t="s">
         <v>65</v>
@@ -43418,7 +43418,7 @@
         <v>88</v>
       </c>
       <c r="D1855" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1855" s="12" t="s">
         <v>65</v>
@@ -43556,7 +43556,7 @@
         <v>76</v>
       </c>
       <c r="D1861" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1861" s="12" t="s">
         <v>67</v>
@@ -43694,7 +43694,7 @@
         <v>76</v>
       </c>
       <c r="D1867" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1867" s="12" t="s">
         <v>68</v>
@@ -44062,7 +44062,7 @@
         <v>64</v>
       </c>
       <c r="D1883" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1883" s="12" t="s">
         <v>65</v>
@@ -44108,7 +44108,7 @@
         <v>64</v>
       </c>
       <c r="D1885" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1885" s="12" t="s">
         <v>68</v>
@@ -44453,7 +44453,7 @@
         <v>59</v>
       </c>
       <c r="D1900" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1900" s="12" t="s">
         <v>61</v>
@@ -44614,7 +44614,7 @@
         <v>59</v>
       </c>
       <c r="D1907" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1907" s="12" t="s">
         <v>66</v>
@@ -45097,7 +45097,7 @@
         <v>86</v>
       </c>
       <c r="D1928" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1928" s="12" t="s">
         <v>68</v>
@@ -45373,7 +45373,7 @@
         <v>74</v>
       </c>
       <c r="D1940" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1940" s="12" t="s">
         <v>61</v>
@@ -45557,7 +45557,7 @@
         <v>74</v>
       </c>
       <c r="D1948" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1948" s="12" t="s">
         <v>67</v>
@@ -45718,7 +45718,7 @@
         <v>88</v>
       </c>
       <c r="D1955" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1955" s="12" t="s">
         <v>65</v>
@@ -45787,7 +45787,7 @@
         <v>88</v>
       </c>
       <c r="D1958" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1958" s="12" t="s">
         <v>68</v>
@@ -46178,7 +46178,7 @@
         <v>76</v>
       </c>
       <c r="D1975" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1975" s="12" t="s">
         <v>61</v>
@@ -46270,7 +46270,7 @@
         <v>76</v>
       </c>
       <c r="D1979" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E1979" s="12" t="s">
         <v>66</v>
@@ -46730,7 +46730,7 @@
         <v>64</v>
       </c>
       <c r="D1999" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E1999" s="12" t="s">
         <v>65</v>
@@ -46868,7 +46868,7 @@
         <v>64</v>
       </c>
       <c r="D2005" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2005" s="12" t="s">
         <v>75</v>
@@ -47052,7 +47052,7 @@
         <v>86</v>
       </c>
       <c r="D2013" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2013" s="12" t="s">
         <v>66</v>
@@ -47098,7 +47098,7 @@
         <v>86</v>
       </c>
       <c r="D2015" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2015" s="12" t="s">
         <v>66</v>
@@ -47558,7 +47558,7 @@
         <v>71</v>
       </c>
       <c r="D2035" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2035" s="12" t="s">
         <v>68</v>
@@ -47650,7 +47650,7 @@
         <v>71</v>
       </c>
       <c r="D2039" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2039" s="12" t="s">
         <v>67</v>
@@ -48018,7 +48018,7 @@
         <v>74</v>
       </c>
       <c r="D2055" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2055" s="12" t="s">
         <v>61</v>
@@ -48294,7 +48294,7 @@
         <v>88</v>
       </c>
       <c r="D2067" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2067" s="12" t="s">
         <v>61</v>
@@ -48317,7 +48317,7 @@
         <v>88</v>
       </c>
       <c r="D2068" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2068" s="12" t="s">
         <v>61</v>
@@ -48662,7 +48662,7 @@
         <v>76</v>
       </c>
       <c r="D2083" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2083" s="12" t="s">
         <v>61</v>
@@ -48777,7 +48777,7 @@
         <v>76</v>
       </c>
       <c r="D2088" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2088" s="12" t="s">
         <v>65</v>
@@ -49191,7 +49191,7 @@
         <v>64</v>
       </c>
       <c r="D2106" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2106" s="12" t="s">
         <v>72</v>
@@ -49214,7 +49214,7 @@
         <v>64</v>
       </c>
       <c r="D2107" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2107" s="12" t="s">
         <v>66</v>
@@ -49605,7 +49605,7 @@
         <v>59</v>
       </c>
       <c r="D2124" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2124" s="12" t="s">
         <v>67</v>
@@ -49789,7 +49789,7 @@
         <v>59</v>
       </c>
       <c r="D2132" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2132" s="12" t="s">
         <v>65</v>
@@ -49881,7 +49881,7 @@
         <v>86</v>
       </c>
       <c r="D2136" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2136" s="12" t="s">
         <v>77</v>
@@ -50042,7 +50042,7 @@
         <v>86</v>
       </c>
       <c r="D2143" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2143" s="12" t="s">
         <v>61</v>
@@ -50203,7 +50203,7 @@
         <v>71</v>
       </c>
       <c r="D2150" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2150" s="12" t="s">
         <v>61</v>
@@ -50318,7 +50318,7 @@
         <v>71</v>
       </c>
       <c r="D2155" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2155" s="12" t="s">
         <v>72</v>
@@ -50525,7 +50525,7 @@
         <v>74</v>
       </c>
       <c r="D2164" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2164" s="12" t="s">
         <v>67</v>
@@ -50893,7 +50893,7 @@
         <v>76</v>
       </c>
       <c r="D2180" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2180" s="12" t="s">
         <v>66</v>
@@ -50939,7 +50939,7 @@
         <v>76</v>
       </c>
       <c r="D2182" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2182" s="12" t="s">
         <v>65</v>
@@ -51123,7 +51123,7 @@
         <v>64</v>
       </c>
       <c r="D2190" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2190" s="12" t="s">
         <v>66</v>
@@ -51192,7 +51192,7 @@
         <v>64</v>
       </c>
       <c r="D2193" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2193" s="12" t="s">
         <v>72</v>
@@ -51468,7 +51468,7 @@
         <v>71</v>
       </c>
       <c r="D2205" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2205" s="12" t="s">
         <v>61</v>
@@ -51790,7 +51790,7 @@
         <v>76</v>
       </c>
       <c r="D2219" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2219" s="12" t="s">
         <v>66</v>
@@ -52135,7 +52135,7 @@
         <v>59</v>
       </c>
       <c r="D2234" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2234" s="12" t="s">
         <v>61</v>
@@ -52342,7 +52342,7 @@
         <v>86</v>
       </c>
       <c r="D2243" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2243" s="12" t="s">
         <v>72</v>
@@ -52641,7 +52641,7 @@
         <v>86</v>
       </c>
       <c r="D2256" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2256" s="12" t="s">
         <v>68</v>
@@ -52664,7 +52664,7 @@
         <v>86</v>
       </c>
       <c r="D2257" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2257" s="12" t="s">
         <v>68</v>
@@ -52756,7 +52756,7 @@
         <v>71</v>
       </c>
       <c r="D2261" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2261" s="12" t="s">
         <v>68</v>
@@ -53009,7 +53009,7 @@
         <v>71</v>
       </c>
       <c r="D2272" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2272" s="12" t="s">
         <v>68</v>
@@ -53078,7 +53078,7 @@
         <v>88</v>
       </c>
       <c r="D2275" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2275" s="12" t="s">
         <v>68</v>
@@ -53308,7 +53308,7 @@
         <v>88</v>
       </c>
       <c r="D2285" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2285" s="12" t="s">
         <v>75</v>
@@ -53515,7 +53515,7 @@
         <v>76</v>
       </c>
       <c r="D2294" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2294" s="12" t="s">
         <v>65</v>
@@ -53975,7 +53975,7 @@
         <v>64</v>
       </c>
       <c r="D2314" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2314" s="12" t="s">
         <v>68</v>
@@ -54021,7 +54021,7 @@
         <v>64</v>
       </c>
       <c r="D2316" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2316" s="12" t="s">
         <v>68</v>
@@ -54159,7 +54159,7 @@
         <v>64</v>
       </c>
       <c r="D2322" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2322" s="12" t="s">
         <v>65</v>
@@ -54389,7 +54389,7 @@
         <v>64</v>
       </c>
       <c r="D2332" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2332" s="12" t="s">
         <v>61</v>
@@ -54826,7 +54826,7 @@
         <v>59</v>
       </c>
       <c r="D2351" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2351" s="12" t="s">
         <v>68</v>
@@ -54918,7 +54918,7 @@
         <v>59</v>
       </c>
       <c r="D2355" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2355" s="12" t="s">
         <v>68</v>
@@ -55332,7 +55332,7 @@
         <v>59</v>
       </c>
       <c r="D2373" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2373" s="12" t="s">
         <v>61</v>
@@ -55424,7 +55424,7 @@
         <v>59</v>
       </c>
       <c r="D2377" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2377" s="12" t="s">
         <v>65</v>
@@ -55585,7 +55585,7 @@
         <v>86</v>
       </c>
       <c r="D2384" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2384" s="12" t="s">
         <v>68</v>
@@ -55654,7 +55654,7 @@
         <v>86</v>
       </c>
       <c r="D2387" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2387" s="12" t="s">
         <v>68</v>
@@ -55953,7 +55953,7 @@
         <v>86</v>
       </c>
       <c r="D2400" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2400" s="12" t="s">
         <v>61</v>
@@ -55999,7 +55999,7 @@
         <v>86</v>
       </c>
       <c r="D2402" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2402" s="12" t="s">
         <v>65</v>
@@ -56206,7 +56206,7 @@
         <v>71</v>
       </c>
       <c r="D2411" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2411" s="12" t="s">
         <v>61</v>
@@ -56413,7 +56413,7 @@
         <v>88</v>
       </c>
       <c r="D2420" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2420" s="12" t="s">
         <v>65</v>
@@ -56436,7 +56436,7 @@
         <v>88</v>
       </c>
       <c r="D2421" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2421" s="12" t="s">
         <v>65</v>
@@ -56620,7 +56620,7 @@
         <v>76</v>
       </c>
       <c r="D2429" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2429" s="12" t="s">
         <v>65</v>
@@ -56643,7 +56643,7 @@
         <v>76</v>
       </c>
       <c r="D2430" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2430" s="12" t="s">
         <v>61</v>
@@ -57034,7 +57034,7 @@
         <v>64</v>
       </c>
       <c r="D2447" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2447" s="12" t="s">
         <v>61</v>
@@ -57517,7 +57517,7 @@
         <v>59</v>
       </c>
       <c r="D2468" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2468" s="12" t="s">
         <v>67</v>
@@ -57862,7 +57862,7 @@
         <v>71</v>
       </c>
       <c r="D2483" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2483" s="12" t="s">
         <v>65</v>
@@ -58184,7 +58184,7 @@
         <v>74</v>
       </c>
       <c r="D2497" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2497" s="12" t="s">
         <v>67</v>
@@ -58713,7 +58713,7 @@
         <v>88</v>
       </c>
       <c r="D2520" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2520" s="12" t="s">
         <v>65</v>
@@ -58897,7 +58897,7 @@
         <v>76</v>
       </c>
       <c r="D2528" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2528" s="12" t="s">
         <v>67</v>
@@ -59196,7 +59196,7 @@
         <v>59</v>
       </c>
       <c r="D2541" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2541" s="12" t="s">
         <v>65</v>
@@ -59725,7 +59725,7 @@
         <v>86</v>
       </c>
       <c r="D2564" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2564" s="12" t="s">
         <v>65</v>
@@ -60116,7 +60116,7 @@
         <v>71</v>
       </c>
       <c r="D2581" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2581" s="12" t="s">
         <v>65</v>
@@ -60461,7 +60461,7 @@
         <v>59</v>
       </c>
       <c r="D2596" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2596" s="12" t="s">
         <v>61</v>
@@ -60875,7 +60875,7 @@
         <v>86</v>
       </c>
       <c r="D2614" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2614" s="12" t="s">
         <v>65</v>
@@ -61059,7 +61059,7 @@
         <v>86</v>
       </c>
       <c r="D2622" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2622" s="12" t="s">
         <v>61</v>
@@ -61220,7 +61220,7 @@
         <v>71</v>
       </c>
       <c r="D2629" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2629" s="12" t="s">
         <v>65</v>
@@ -61818,7 +61818,7 @@
         <v>74</v>
       </c>
       <c r="D2655" s="12" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E2655" s="12" t="s">
         <v>61</v>
@@ -61910,7 +61910,7 @@
         <v>74</v>
       </c>
       <c r="D2659" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2659" s="12" t="s">
         <v>68</v>
@@ -62025,7 +62025,7 @@
         <v>88</v>
       </c>
       <c r="D2664" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2664" s="12" t="s">
         <v>65</v>
@@ -62347,7 +62347,7 @@
         <v>64</v>
       </c>
       <c r="D2678" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2678" s="12" t="s">
         <v>61</v>
@@ -62600,7 +62600,7 @@
         <v>59</v>
       </c>
       <c r="D2689" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2689" s="12" t="s">
         <v>68</v>
@@ -62876,7 +62876,7 @@
         <v>71</v>
       </c>
       <c r="D2701" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2701" s="12" t="s">
         <v>66</v>
@@ -63060,7 +63060,7 @@
         <v>71</v>
       </c>
       <c r="D2709" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2709" s="12" t="s">
         <v>61</v>
@@ -63221,7 +63221,7 @@
         <v>76</v>
       </c>
       <c r="D2716" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2716" s="12" t="s">
         <v>68</v>
@@ -63796,7 +63796,7 @@
         <v>64</v>
       </c>
       <c r="D2741" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2741" s="12" t="s">
         <v>67</v>
@@ -64118,7 +64118,7 @@
         <v>59</v>
       </c>
       <c r="D2755" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2755" s="12" t="s">
         <v>61</v>
@@ -64279,7 +64279,7 @@
         <v>86</v>
       </c>
       <c r="D2762" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2762" s="12" t="s">
         <v>61</v>
@@ -64532,7 +64532,7 @@
         <v>71</v>
       </c>
       <c r="D2773" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2773" s="12" t="s">
         <v>61</v>
@@ -64877,7 +64877,7 @@
         <v>88</v>
       </c>
       <c r="D2788" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2788" s="12" t="s">
         <v>68</v>
@@ -64992,7 +64992,7 @@
         <v>76</v>
       </c>
       <c r="D2793" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2793" s="12" t="s">
         <v>67</v>
@@ -65153,7 +65153,7 @@
         <v>64</v>
       </c>
       <c r="D2800" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2800" s="12" t="s">
         <v>75</v>
@@ -65337,7 +65337,7 @@
         <v>86</v>
       </c>
       <c r="D2808" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2808" s="12" t="s">
         <v>61</v>
@@ -65613,7 +65613,7 @@
         <v>71</v>
       </c>
       <c r="D2820" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2820" s="12" t="s">
         <v>66</v>
@@ -66050,7 +66050,7 @@
         <v>76</v>
       </c>
       <c r="D2839" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2839" s="12" t="s">
         <v>68</v>
@@ -66303,7 +66303,7 @@
         <v>64</v>
       </c>
       <c r="D2850" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2850" s="12" t="s">
         <v>65</v>
@@ -66832,7 +66832,7 @@
         <v>71</v>
       </c>
       <c r="D2873" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2873" s="12" t="s">
         <v>66</v>
@@ -67154,7 +67154,7 @@
         <v>76</v>
       </c>
       <c r="D2887" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2887" s="12" t="s">
         <v>68</v>
@@ -67407,7 +67407,7 @@
         <v>64</v>
       </c>
       <c r="D2898" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2898" s="12" t="s">
         <v>65</v>
@@ -67499,7 +67499,7 @@
         <v>59</v>
       </c>
       <c r="D2902" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2902" s="12" t="s">
         <v>61</v>
@@ -67706,7 +67706,7 @@
         <v>86</v>
       </c>
       <c r="D2911" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2911" s="12" t="s">
         <v>75</v>
@@ -67890,7 +67890,7 @@
         <v>88</v>
       </c>
       <c r="D2919" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2919" s="12" t="s">
         <v>61</v>
@@ -68051,7 +68051,7 @@
         <v>76</v>
       </c>
       <c r="D2926" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2926" s="12" t="s">
         <v>61</v>
@@ -68327,7 +68327,7 @@
         <v>64</v>
       </c>
       <c r="D2938" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2938" s="12" t="s">
         <v>68</v>
@@ -68465,7 +68465,7 @@
         <v>86</v>
       </c>
       <c r="D2944" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2944" s="12" t="s">
         <v>65</v>
@@ -68603,7 +68603,7 @@
         <v>71</v>
       </c>
       <c r="D2950" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2950" s="12" t="s">
         <v>66</v>
@@ -68948,7 +68948,7 @@
         <v>59</v>
       </c>
       <c r="D2965" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2965" s="12" t="s">
         <v>61</v>
@@ -69063,7 +69063,7 @@
         <v>86</v>
       </c>
       <c r="D2970" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2970" s="12" t="s">
         <v>68</v>
@@ -69546,7 +69546,7 @@
         <v>76</v>
       </c>
       <c r="D2991" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E2991" s="12" t="s">
         <v>65</v>
@@ -69753,7 +69753,7 @@
         <v>64</v>
       </c>
       <c r="D3000" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3000" s="12" t="s">
         <v>68</v>
@@ -69868,7 +69868,7 @@
         <v>59</v>
       </c>
       <c r="D3005" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3005" s="12" t="s">
         <v>67</v>
@@ -70489,7 +70489,7 @@
         <v>88</v>
       </c>
       <c r="D3032" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3032" s="12" t="s">
         <v>65</v>
@@ -70558,7 +70558,7 @@
         <v>88</v>
       </c>
       <c r="D3035" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3035" s="12" t="s">
         <v>61</v>
@@ -70581,7 +70581,7 @@
         <v>76</v>
       </c>
       <c r="D3036" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3036" s="12" t="s">
         <v>68</v>
@@ -70650,7 +70650,7 @@
         <v>64</v>
       </c>
       <c r="D3039" s="12" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E3039" s="12" t="s">
         <v>75</v>
@@ -72169,7 +72169,7 @@
         <v>39</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E25" s="3" t="s">
         <v>5</v>
@@ -72177,10 +72177,10 @@
     </row>
     <row r="26">
       <c r="A26" s="1" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" s="3" t="s">
         <v>5</v>

--- a/data/rpe_femenil.xlsx
+++ b/data/rpe_femenil.xlsx
@@ -143,6 +143,9 @@
     <t>Sarah Luebbert</t>
   </si>
   <si>
+    <t>Marca temporal</t>
+  </si>
+  <si>
     <t>Aylin</t>
   </si>
   <si>
@@ -168,9 +171,6 @@
   </si>
   <si>
     <t>Jordan Brewster</t>
-  </si>
-  <si>
-    <t>Marca temporal</t>
   </si>
   <si>
     <t>Puntuación</t>
@@ -767,7 +767,7 @@
   <sheetData>
     <row r="1" ht="22.5" customHeight="1">
       <c r="A1" s="4" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
       <c r="B1" s="4" t="s">
         <v>53</v>
@@ -3306,7 +3306,7 @@
         <v>64</v>
       </c>
       <c r="D111" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E111" s="12" t="s">
         <v>65</v>
@@ -3513,7 +3513,7 @@
         <v>59</v>
       </c>
       <c r="D120" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E120" s="12" t="s">
         <v>68</v>
@@ -3973,7 +3973,7 @@
         <v>71</v>
       </c>
       <c r="D140" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E140" s="12" t="s">
         <v>66</v>
@@ -4640,7 +4640,7 @@
         <v>76</v>
       </c>
       <c r="D169" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E169" s="12" t="s">
         <v>61</v>
@@ -4870,7 +4870,7 @@
         <v>64</v>
       </c>
       <c r="D179" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E179" s="12" t="s">
         <v>75</v>
@@ -5537,7 +5537,7 @@
         <v>86</v>
       </c>
       <c r="D208" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E208" s="12" t="s">
         <v>66</v>
@@ -6181,7 +6181,7 @@
         <v>88</v>
       </c>
       <c r="D236" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E236" s="12" t="s">
         <v>61</v>
@@ -6411,7 +6411,7 @@
         <v>76</v>
       </c>
       <c r="D246" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E246" s="12" t="s">
         <v>61</v>
@@ -7515,7 +7515,7 @@
         <v>88</v>
       </c>
       <c r="D294" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E294" s="12" t="s">
         <v>68</v>
@@ -7860,7 +7860,7 @@
         <v>76</v>
       </c>
       <c r="D309" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E309" s="12" t="s">
         <v>61</v>
@@ -8343,7 +8343,7 @@
         <v>64</v>
       </c>
       <c r="D330" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E330" s="12" t="s">
         <v>67</v>
@@ -8504,7 +8504,7 @@
         <v>86</v>
       </c>
       <c r="D337" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E337" s="12" t="s">
         <v>66</v>
@@ -8619,7 +8619,7 @@
         <v>86</v>
       </c>
       <c r="D342" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E342" s="12" t="s">
         <v>61</v>
@@ -8780,7 +8780,7 @@
         <v>71</v>
       </c>
       <c r="D349" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E349" s="12" t="s">
         <v>61</v>
@@ -9286,7 +9286,7 @@
         <v>76</v>
       </c>
       <c r="D371" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E371" s="12" t="s">
         <v>61</v>
@@ -9562,7 +9562,7 @@
         <v>64</v>
       </c>
       <c r="D383" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E383" s="12" t="s">
         <v>72</v>
@@ -11011,7 +11011,7 @@
         <v>64</v>
       </c>
       <c r="D446" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E446" s="12" t="s">
         <v>72</v>
@@ -11172,7 +11172,7 @@
         <v>86</v>
       </c>
       <c r="D453" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E453" s="12" t="s">
         <v>66</v>
@@ -11356,7 +11356,7 @@
         <v>71</v>
       </c>
       <c r="D461" s="12" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="E461" s="12" t="s">
         <v>72</v>
@@ -11954,7 +11954,7 @@
         <v>74</v>
       </c>
       <c r="D487" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E487" s="12" t="s">
         <v>68</v>
@@ -12046,7 +12046,7 @@
         <v>64</v>
       </c>
       <c r="D491" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E491" s="12" t="s">
         <v>61</v>
@@ -12598,7 +12598,7 @@
         <v>86</v>
       </c>
       <c r="D515" s="12" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E515" s="12" t="s">
         <v>61</v>
@@ -12897,7 +12897,7 @@
         <v>74</v>
       </c>
       <c r="D528" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E528" s="12" t="s">
         <v>67</v>
@@ -13173,7 +13173,7 @@
         <v>76</v>
       </c>
       <c r="D540" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E540" s="12" t="s">
         <v>66</v>
@@ -13334,7 +13334,7 @@
         <v>64</v>
       </c>
       <c r="D547" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E547" s="12" t="s">
         <v>66</v>
@@ -13403,7 +13403,7 @@
         <v>86</v>
       </c>
       <c r="D550" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E550" s="12" t="s">
         <v>67</v>
@@ -13564,7 +13564,7 @@
         <v>71</v>
       </c>
       <c r="D557" s="12" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E557" s="12" t="s">
         <v>77</v>
@@ -17152,7 +17152,7 @@
         <v>59</v>
       </c>
       <c r="D713" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E713" s="12" t="s">
         <v>68</v>
@@ -18049,7 +18049,7 @@
         <v>88</v>
       </c>
       <c r="D752" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E752" s="12" t="s">
         <v>61</v>
@@ -18923,7 +18923,7 @@
         <v>64</v>
       </c>
       <c r="D790" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E790" s="12" t="s">
         <v>67</v>
@@ -19268,7 +19268,7 @@
         <v>86</v>
       </c>
       <c r="D805" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E805" s="12" t="s">
         <v>61</v>
@@ -19452,7 +19452,7 @@
         <v>86</v>
       </c>
       <c r="D813" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E813" s="12" t="s">
         <v>61</v>
@@ -20809,7 +20809,7 @@
         <v>59</v>
       </c>
       <c r="D872" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E872" s="12" t="s">
         <v>65</v>
@@ -20855,7 +20855,7 @@
         <v>59</v>
       </c>
       <c r="D874" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E874" s="12" t="s">
         <v>68</v>
@@ -21177,7 +21177,7 @@
         <v>86</v>
       </c>
       <c r="D888" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E888" s="12" t="s">
         <v>61</v>
@@ -21269,7 +21269,7 @@
         <v>86</v>
       </c>
       <c r="D892" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E892" s="12" t="s">
         <v>61</v>
@@ -21821,7 +21821,7 @@
         <v>71</v>
       </c>
       <c r="D916" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E916" s="12" t="s">
         <v>61</v>
@@ -21982,7 +21982,7 @@
         <v>71</v>
       </c>
       <c r="D923" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E923" s="12" t="s">
         <v>61</v>
@@ -22672,7 +22672,7 @@
         <v>64</v>
       </c>
       <c r="D953" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E953" s="12" t="s">
         <v>61</v>
@@ -22764,7 +22764,7 @@
         <v>64</v>
       </c>
       <c r="D957" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E957" s="12" t="s">
         <v>61</v>
@@ -23224,7 +23224,7 @@
         <v>59</v>
       </c>
       <c r="D977" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E977" s="12" t="s">
         <v>65</v>
@@ -23293,7 +23293,7 @@
         <v>59</v>
       </c>
       <c r="D980" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E980" s="12" t="s">
         <v>68</v>
@@ -23615,7 +23615,7 @@
         <v>86</v>
       </c>
       <c r="D994" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E994" s="12" t="s">
         <v>66</v>
@@ -24052,7 +24052,7 @@
         <v>71</v>
       </c>
       <c r="D1013" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1013" s="12" t="s">
         <v>66</v>
@@ -24328,7 +24328,7 @@
         <v>71</v>
       </c>
       <c r="D1025" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1025" s="12" t="s">
         <v>66</v>
@@ -24834,7 +24834,7 @@
         <v>88</v>
       </c>
       <c r="D1047" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1047" s="12" t="s">
         <v>65</v>
@@ -24995,7 +24995,7 @@
         <v>88</v>
       </c>
       <c r="D1054" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1054" s="12" t="s">
         <v>68</v>
@@ -25593,7 +25593,7 @@
         <v>76</v>
       </c>
       <c r="D1080" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1080" s="12" t="s">
         <v>61</v>
@@ -25639,7 +25639,7 @@
         <v>76</v>
       </c>
       <c r="D1082" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1082" s="12" t="s">
         <v>66</v>
@@ -26168,7 +26168,7 @@
         <v>64</v>
       </c>
       <c r="D1105" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1105" s="12" t="s">
         <v>66</v>
@@ -26237,7 +26237,7 @@
         <v>64</v>
       </c>
       <c r="D1108" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1108" s="12" t="s">
         <v>65</v>
@@ -26858,7 +26858,7 @@
         <v>71</v>
       </c>
       <c r="D1135" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1135" s="12" t="s">
         <v>61</v>
@@ -26904,7 +26904,7 @@
         <v>71</v>
       </c>
       <c r="D1137" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1137" s="12" t="s">
         <v>61</v>
@@ -27295,7 +27295,7 @@
         <v>74</v>
       </c>
       <c r="D1154" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1154" s="12" t="s">
         <v>66</v>
@@ -27410,7 +27410,7 @@
         <v>74</v>
       </c>
       <c r="D1159" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1159" s="12" t="s">
         <v>66</v>
@@ -28307,7 +28307,7 @@
         <v>64</v>
       </c>
       <c r="D1198" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1198" s="12" t="s">
         <v>65</v>
@@ -28491,7 +28491,7 @@
         <v>64</v>
       </c>
       <c r="D1206" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1206" s="12" t="s">
         <v>68</v>
@@ -28882,7 +28882,7 @@
         <v>59</v>
       </c>
       <c r="D1223" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1223" s="12" t="s">
         <v>67</v>
@@ -28951,7 +28951,7 @@
         <v>59</v>
       </c>
       <c r="D1226" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1226" s="12" t="s">
         <v>61</v>
@@ -29319,7 +29319,7 @@
         <v>86</v>
       </c>
       <c r="D1242" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1242" s="12" t="s">
         <v>61</v>
@@ -29365,7 +29365,7 @@
         <v>86</v>
       </c>
       <c r="D1244" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1244" s="12" t="s">
         <v>61</v>
@@ -29549,7 +29549,7 @@
         <v>86</v>
       </c>
       <c r="D1252" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1252" s="12" t="s">
         <v>61</v>
@@ -29756,7 +29756,7 @@
         <v>71</v>
       </c>
       <c r="D1261" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1261" s="12" t="s">
         <v>66</v>
@@ -29871,7 +29871,7 @@
         <v>71</v>
       </c>
       <c r="D1266" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1266" s="12" t="s">
         <v>66</v>
@@ -30630,7 +30630,7 @@
         <v>76</v>
       </c>
       <c r="D1299" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1299" s="12" t="s">
         <v>65</v>
@@ -30653,7 +30653,7 @@
         <v>76</v>
       </c>
       <c r="D1300" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1300" s="12" t="s">
         <v>65</v>
@@ -31090,7 +31090,7 @@
         <v>64</v>
       </c>
       <c r="D1319" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1319" s="12" t="s">
         <v>65</v>
@@ -31113,7 +31113,7 @@
         <v>64</v>
       </c>
       <c r="D1320" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1320" s="12" t="s">
         <v>61</v>
@@ -31573,7 +31573,7 @@
         <v>59</v>
       </c>
       <c r="D1340" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1340" s="12" t="s">
         <v>65</v>
@@ -31596,7 +31596,7 @@
         <v>59</v>
       </c>
       <c r="D1341" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1341" s="12" t="s">
         <v>61</v>
@@ -31734,7 +31734,7 @@
         <v>71</v>
       </c>
       <c r="D1347" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1347" s="12" t="s">
         <v>66</v>
@@ -31918,7 +31918,7 @@
         <v>71</v>
       </c>
       <c r="D1355" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1355" s="12" t="s">
         <v>66</v>
@@ -32355,7 +32355,7 @@
         <v>64</v>
       </c>
       <c r="D1374" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1374" s="12" t="s">
         <v>66</v>
@@ -32516,7 +32516,7 @@
         <v>64</v>
       </c>
       <c r="D1381" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1381" s="12" t="s">
         <v>61</v>
@@ -32769,7 +32769,7 @@
         <v>88</v>
       </c>
       <c r="D1392" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1392" s="12" t="s">
         <v>61</v>
@@ -32838,7 +32838,7 @@
         <v>88</v>
       </c>
       <c r="D1395" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1395" s="12" t="s">
         <v>61</v>
@@ -32861,7 +32861,7 @@
         <v>88</v>
       </c>
       <c r="D1396" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1396" s="12" t="s">
         <v>61</v>
@@ -33091,7 +33091,7 @@
         <v>76</v>
       </c>
       <c r="D1406" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1406" s="12" t="s">
         <v>65</v>
@@ -33298,7 +33298,7 @@
         <v>59</v>
       </c>
       <c r="D1415" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1415" s="12" t="s">
         <v>65</v>
@@ -33528,7 +33528,7 @@
         <v>86</v>
       </c>
       <c r="D1425" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1425" s="12" t="s">
         <v>61</v>
@@ -33666,7 +33666,7 @@
         <v>86</v>
       </c>
       <c r="D1431" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1431" s="12" t="s">
         <v>61</v>
@@ -34172,7 +34172,7 @@
         <v>74</v>
       </c>
       <c r="D1453" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1453" s="12" t="s">
         <v>72</v>
@@ -34333,7 +34333,7 @@
         <v>74</v>
       </c>
       <c r="D1460" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1460" s="12" t="s">
         <v>61</v>
@@ -34632,7 +34632,7 @@
         <v>88</v>
       </c>
       <c r="D1473" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1473" s="12" t="s">
         <v>66</v>
@@ -34678,7 +34678,7 @@
         <v>88</v>
       </c>
       <c r="D1475" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1475" s="12" t="s">
         <v>66</v>
@@ -35322,7 +35322,7 @@
         <v>59</v>
       </c>
       <c r="D1503" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1503" s="12" t="s">
         <v>66</v>
@@ -35345,7 +35345,7 @@
         <v>59</v>
       </c>
       <c r="D1504" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1504" s="12" t="s">
         <v>66</v>
@@ -35690,7 +35690,7 @@
         <v>86</v>
       </c>
       <c r="D1519" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1519" s="12" t="s">
         <v>66</v>
@@ -35736,7 +35736,7 @@
         <v>71</v>
       </c>
       <c r="D1521" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1521" s="12" t="s">
         <v>93</v>
@@ -36219,7 +36219,7 @@
         <v>74</v>
       </c>
       <c r="D1542" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1542" s="12" t="s">
         <v>61</v>
@@ -36748,7 +36748,7 @@
         <v>59</v>
       </c>
       <c r="D1565" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1565" s="12" t="s">
         <v>65</v>
@@ -36909,7 +36909,7 @@
         <v>59</v>
       </c>
       <c r="D1572" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1572" s="12" t="s">
         <v>61</v>
@@ -37277,7 +37277,7 @@
         <v>86</v>
       </c>
       <c r="D1588" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1588" s="12" t="s">
         <v>61</v>
@@ -37438,7 +37438,7 @@
         <v>86</v>
       </c>
       <c r="D1595" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1595" s="12" t="s">
         <v>61</v>
@@ -37645,7 +37645,7 @@
         <v>71</v>
       </c>
       <c r="D1604" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1604" s="12" t="s">
         <v>66</v>
@@ -37760,7 +37760,7 @@
         <v>71</v>
       </c>
       <c r="D1609" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1609" s="12" t="s">
         <v>66</v>
@@ -38036,7 +38036,7 @@
         <v>74</v>
       </c>
       <c r="D1621" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1621" s="12" t="s">
         <v>65</v>
@@ -38381,7 +38381,7 @@
         <v>88</v>
       </c>
       <c r="D1636" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1636" s="12" t="s">
         <v>65</v>
@@ -38565,7 +38565,7 @@
         <v>88</v>
       </c>
       <c r="D1644" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1644" s="12" t="s">
         <v>66</v>
@@ -38956,7 +38956,7 @@
         <v>64</v>
       </c>
       <c r="D1661" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1661" s="12" t="s">
         <v>68</v>
@@ -39646,7 +39646,7 @@
         <v>88</v>
       </c>
       <c r="D1691" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1691" s="12" t="s">
         <v>66</v>
@@ -40037,7 +40037,7 @@
         <v>76</v>
       </c>
       <c r="D1708" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1708" s="12" t="s">
         <v>65</v>
@@ -40060,7 +40060,7 @@
         <v>76</v>
       </c>
       <c r="D1709" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1709" s="12" t="s">
         <v>66</v>
@@ -40405,7 +40405,7 @@
         <v>64</v>
       </c>
       <c r="D1724" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1724" s="12" t="s">
         <v>65</v>
@@ -40566,7 +40566,7 @@
         <v>64</v>
       </c>
       <c r="D1731" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1731" s="12" t="s">
         <v>65</v>
@@ -40704,7 +40704,7 @@
         <v>59</v>
       </c>
       <c r="D1737" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1737" s="12" t="s">
         <v>61</v>
@@ -40842,7 +40842,7 @@
         <v>59</v>
       </c>
       <c r="D1743" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1743" s="12" t="s">
         <v>61</v>
@@ -41210,7 +41210,7 @@
         <v>86</v>
       </c>
       <c r="D1759" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1759" s="12" t="s">
         <v>61</v>
@@ -41348,7 +41348,7 @@
         <v>71</v>
       </c>
       <c r="D1765" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1765" s="12" t="s">
         <v>61</v>
@@ -41532,7 +41532,7 @@
         <v>71</v>
       </c>
       <c r="D1773" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1773" s="12" t="s">
         <v>65</v>
@@ -41808,7 +41808,7 @@
         <v>64</v>
       </c>
       <c r="D1785" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1785" s="12" t="s">
         <v>66</v>
@@ -42038,7 +42038,7 @@
         <v>59</v>
       </c>
       <c r="D1795" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1795" s="12" t="s">
         <v>67</v>
@@ -42107,7 +42107,7 @@
         <v>59</v>
       </c>
       <c r="D1798" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1798" s="12" t="s">
         <v>75</v>
@@ -42291,7 +42291,7 @@
         <v>74</v>
       </c>
       <c r="D1806" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1806" s="12" t="s">
         <v>67</v>
@@ -42452,7 +42452,7 @@
         <v>74</v>
       </c>
       <c r="D1813" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1813" s="12" t="s">
         <v>67</v>
@@ -42659,7 +42659,7 @@
         <v>76</v>
       </c>
       <c r="D1822" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1822" s="12" t="s">
         <v>61</v>
@@ -42912,7 +42912,7 @@
         <v>64</v>
       </c>
       <c r="D1833" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1833" s="12" t="s">
         <v>65</v>
@@ -43027,7 +43027,7 @@
         <v>64</v>
       </c>
       <c r="D1838" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1838" s="12" t="s">
         <v>61</v>
@@ -43142,7 +43142,7 @@
         <v>88</v>
       </c>
       <c r="D1843" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1843" s="12" t="s">
         <v>68</v>
@@ -43671,7 +43671,7 @@
         <v>76</v>
       </c>
       <c r="D1866" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1866" s="12" t="s">
         <v>65</v>
@@ -43832,7 +43832,7 @@
         <v>76</v>
       </c>
       <c r="D1873" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1873" s="12" t="s">
         <v>65</v>
@@ -44085,7 +44085,7 @@
         <v>64</v>
       </c>
       <c r="D1884" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1884" s="12" t="s">
         <v>61</v>
@@ -44269,7 +44269,7 @@
         <v>64</v>
       </c>
       <c r="D1892" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1892" s="12" t="s">
         <v>61</v>
@@ -44660,7 +44660,7 @@
         <v>59</v>
       </c>
       <c r="D1909" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1909" s="12" t="s">
         <v>61</v>
@@ -45005,7 +45005,7 @@
         <v>86</v>
       </c>
       <c r="D1924" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1924" s="12" t="s">
         <v>67</v>
@@ -45419,7 +45419,7 @@
         <v>74</v>
       </c>
       <c r="D1942" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1942" s="12" t="s">
         <v>61</v>
@@ -45580,7 +45580,7 @@
         <v>74</v>
       </c>
       <c r="D1949" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1949" s="12" t="s">
         <v>61</v>
@@ -45833,7 +45833,7 @@
         <v>88</v>
       </c>
       <c r="D1960" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1960" s="12" t="s">
         <v>61</v>
@@ -45971,7 +45971,7 @@
         <v>88</v>
       </c>
       <c r="D1966" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1966" s="12" t="s">
         <v>66</v>
@@ -46408,7 +46408,7 @@
         <v>76</v>
       </c>
       <c r="D1985" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E1985" s="12" t="s">
         <v>61</v>
@@ -46454,7 +46454,7 @@
         <v>76</v>
       </c>
       <c r="D1987" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E1987" s="12" t="s">
         <v>66</v>
@@ -46891,7 +46891,7 @@
         <v>59</v>
       </c>
       <c r="D2006" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2006" s="12" t="s">
         <v>65</v>
@@ -47121,7 +47121,7 @@
         <v>86</v>
       </c>
       <c r="D2016" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2016" s="12" t="s">
         <v>66</v>
@@ -47374,7 +47374,7 @@
         <v>86</v>
       </c>
       <c r="D2027" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2027" s="12" t="s">
         <v>66</v>
@@ -47604,7 +47604,7 @@
         <v>71</v>
       </c>
       <c r="D2037" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2037" s="12" t="s">
         <v>77</v>
@@ -47673,7 +47673,7 @@
         <v>71</v>
       </c>
       <c r="D2040" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2040" s="12" t="s">
         <v>65</v>
@@ -48133,7 +48133,7 @@
         <v>74</v>
       </c>
       <c r="D2060" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2060" s="12" t="s">
         <v>61</v>
@@ -48501,7 +48501,7 @@
         <v>88</v>
       </c>
       <c r="D2076" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2076" s="12" t="s">
         <v>61</v>
@@ -49237,7 +49237,7 @@
         <v>64</v>
       </c>
       <c r="D2108" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2108" s="12" t="s">
         <v>61</v>
@@ -49260,7 +49260,7 @@
         <v>64</v>
       </c>
       <c r="D2109" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2109" s="12" t="s">
         <v>66</v>
@@ -49628,7 +49628,7 @@
         <v>59</v>
       </c>
       <c r="D2125" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2125" s="12" t="s">
         <v>68</v>
@@ -49674,7 +49674,7 @@
         <v>59</v>
       </c>
       <c r="D2127" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2127" s="12" t="s">
         <v>65</v>
@@ -50111,7 +50111,7 @@
         <v>86</v>
       </c>
       <c r="D2146" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2146" s="12" t="s">
         <v>61</v>
@@ -51537,7 +51537,7 @@
         <v>71</v>
       </c>
       <c r="D2208" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2208" s="12" t="s">
         <v>66</v>
@@ -51836,7 +51836,7 @@
         <v>76</v>
       </c>
       <c r="D2221" s="12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E2221" s="12" t="s">
         <v>72</v>
@@ -52687,7 +52687,7 @@
         <v>86</v>
       </c>
       <c r="D2258" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2258" s="12" t="s">
         <v>75</v>
@@ -52986,7 +52986,7 @@
         <v>71</v>
       </c>
       <c r="D2271" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2271" s="12" t="s">
         <v>65</v>
@@ -53377,7 +53377,7 @@
         <v>88</v>
       </c>
       <c r="D2288" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2288" s="12" t="s">
         <v>75</v>
@@ -53791,7 +53791,7 @@
         <v>64</v>
       </c>
       <c r="D2306" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2306" s="12" t="s">
         <v>68</v>
@@ -54642,7 +54642,7 @@
         <v>64</v>
       </c>
       <c r="D2343" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2343" s="12" t="s">
         <v>61</v>
@@ -54734,7 +54734,7 @@
         <v>59</v>
       </c>
       <c r="D2347" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2347" s="12" t="s">
         <v>67</v>
@@ -55769,7 +55769,7 @@
         <v>86</v>
       </c>
       <c r="D2392" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2392" s="12" t="s">
         <v>68</v>
@@ -60691,7 +60691,7 @@
         <v>59</v>
       </c>
       <c r="D2606" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2606" s="12" t="s">
         <v>61</v>
@@ -61588,7 +61588,7 @@
         <v>71</v>
       </c>
       <c r="D2645" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2645" s="12" t="s">
         <v>67</v>
@@ -62807,7 +62807,7 @@
         <v>86</v>
       </c>
       <c r="D2698" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2698" s="12" t="s">
         <v>61</v>
@@ -63175,7 +63175,7 @@
         <v>76</v>
       </c>
       <c r="D2714" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2714" s="12" t="s">
         <v>65</v>
@@ -63842,7 +63842,7 @@
         <v>64</v>
       </c>
       <c r="D2743" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2743" s="12" t="s">
         <v>65</v>
@@ -64049,7 +64049,7 @@
         <v>59</v>
       </c>
       <c r="D2752" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2752" s="12" t="s">
         <v>65</v>
@@ -64900,7 +64900,7 @@
         <v>88</v>
       </c>
       <c r="D2789" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2789" s="12" t="s">
         <v>61</v>
@@ -66188,7 +66188,7 @@
         <v>64</v>
       </c>
       <c r="D2845" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2845" s="12" t="s">
         <v>65</v>
@@ -66694,7 +66694,7 @@
         <v>59</v>
       </c>
       <c r="D2867" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2867" s="12" t="s">
         <v>68</v>
@@ -66970,7 +66970,7 @@
         <v>74</v>
       </c>
       <c r="D2879" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2879" s="12" t="s">
         <v>68</v>
@@ -67798,7 +67798,7 @@
         <v>88</v>
       </c>
       <c r="D2915" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2915" s="12" t="s">
         <v>61</v>
@@ -68120,7 +68120,7 @@
         <v>76</v>
       </c>
       <c r="D2929" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2929" s="12" t="s">
         <v>65</v>
@@ -68350,7 +68350,7 @@
         <v>64</v>
       </c>
       <c r="D2939" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2939" s="12" t="s">
         <v>65</v>
@@ -68488,7 +68488,7 @@
         <v>86</v>
       </c>
       <c r="D2945" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2945" s="12" t="s">
         <v>61</v>
@@ -68856,7 +68856,7 @@
         <v>59</v>
       </c>
       <c r="D2961" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2961" s="12" t="s">
         <v>61</v>
@@ -69155,7 +69155,7 @@
         <v>71</v>
       </c>
       <c r="D2974" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2974" s="12" t="s">
         <v>66</v>
@@ -69615,7 +69615,7 @@
         <v>76</v>
       </c>
       <c r="D2994" s="12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E2994" s="12" t="s">
         <v>61</v>
@@ -72211,10 +72211,10 @@
     </row>
     <row r="27">
       <c r="A27" s="1" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E27" s="3" t="s">
         <v>5</v>
@@ -72222,10 +72222,10 @@
     </row>
     <row r="28">
       <c r="A28" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E28" s="3" t="s">
         <v>5</v>
@@ -72233,10 +72233,10 @@
     </row>
     <row r="29">
       <c r="A29" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E29" s="3" t="s">
         <v>5</v>
@@ -72244,10 +72244,10 @@
     </row>
     <row r="30">
       <c r="A30" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E30" s="3" t="s">
         <v>5</v>
@@ -72255,10 +72255,10 @@
     </row>
     <row r="31">
       <c r="A31" s="1" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E31" s="3" t="s">
         <v>5</v>
@@ -72266,10 +72266,10 @@
     </row>
     <row r="32">
       <c r="A32" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="E32" s="3" t="s">
         <v>5</v>
@@ -72277,10 +72277,10 @@
     </row>
     <row r="33">
       <c r="A33" s="2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B33" s="2" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="E33" s="3" t="s">
         <v>5</v>
